--- a/artfynd/A 17074-2024 artfynd.xlsx
+++ b/artfynd/A 17074-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91173123</v>
+        <v>117947862</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korgvideodling N om Lögaredammen, Nrk</t>
+          <t>Skogshyddan, SO om, V om Latorps gård, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498988.0374287562</v>
+        <v>498799</v>
       </c>
       <c r="R2" t="n">
-        <v>6572213.880340368</v>
+        <v>6572395</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +772,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Artdokumentation i samband med framtagande av Vinteråsens NR 2018-2020</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91173119</v>
+        <v>60885569</v>
       </c>
       <c r="B3" t="n">
-        <v>104654</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +795,52 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220015</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Campanula latifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korgvideodling N om Lögaredammen, Nrk</t>
+          <t>Skogshyddan, SO om, V om Latorps gård, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498988.0374287562</v>
+        <v>498799</v>
       </c>
       <c r="R3" t="n">
-        <v>6572213.880340368</v>
+        <v>6572395</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>vägdike vid vägkorsning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,73 +889,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Artdokumentation i samband med framtagande av Vinteråsens NR 2018-2020</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98073573</v>
+        <v>91173123</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Latorp, Nrk</t>
+          <t>Korgvideodling N om Lögaredammen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499044.3372064246</v>
+        <v>498988</v>
       </c>
       <c r="R4" t="n">
-        <v>6572232.257245803</v>
+        <v>6572214</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,34 +964,14 @@
           <t>Tysslinge</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>A0FDB9B1-BB09-4C68-BDD5-80567055BB6D</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2006-08-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2006-08-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens alléinventering, Gröna jobb, 2005-2006</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,48 +986,43 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Henrik Josefsson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Artdokumentation i samband med framtagande av Vinteråsens NR 2018-2020</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98073572</v>
+        <v>91173119</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107719</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>220015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Campanula latifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,24 +1030,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Latorp, Nrk</t>
+          <t>Korgvideodling N om Lögaredammen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498930.2166031561</v>
+        <v>498988</v>
       </c>
       <c r="R5" t="n">
-        <v>6572248.12473591</v>
+        <v>6572214</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,34 +1065,14 @@
           <t>Tysslinge</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>96FC7F40-0B69-458C-ADC3-ED426292C0FE</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2006-08-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2006-08-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens alléinventering, Gröna jobb, 2005-2006</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,15 +1087,595 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Artdokumentation i samband med framtagande av Vinteråsens NR 2018-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117819598</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogshyttan SO om, V om Latorps gård, Norra Latorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498784</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6572407</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Längs vägen, längs en sträcka av 5-10 meter.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>gles lövskog med bl.a. bok</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98073572</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Latorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>498930</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6572248</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>96FC7F40-0B69-458C-ADC3-ED426292C0FE</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2006-08-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2006-08-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens alléinventering, Gröna jobb, 2005-2006</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Henrik Josefsson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Via Henrik Josefsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>98073573</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Latorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>499044</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6572233</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A0FDB9B1-BB09-4C68-BDD5-80567055BB6D</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2006-08-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2006-08-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens alléinventering, Gröna jobb, 2005-2006</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>98074481</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Latorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>498759</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6572428</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6E845720-7E19-40E0-99AA-4C693470A8D5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2006-08-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2006-08-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens alléinventering, Gröna jobb, 2005-2006</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>98074482</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Latorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>499075</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6572343</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>AD02A0D2-5B4B-4EB3-AAB8-508CBA55304D</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2006-08-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2006-08-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens alléinventering, Gröna jobb, 2005-2006</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 17074-2024 artfynd.xlsx
+++ b/artfynd/A 17074-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117947862</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60885569</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
           <t>Artdokumentation i samband med framtagande av Vinteråsens NR 2018-2020</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91173123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
           <t>Artdokumentation i samband med framtagande av Vinteråsens NR 2018-2020</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91173119</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117819598</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98073572</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98073573</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98074481</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,8 +1725,24 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98074482</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>